--- a/data/significant_moderators.xlsx
+++ b/data/significant_moderators.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,92 +448,2705 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Versicherte</t>
+          <t>Alter_70_Jahre</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.49862535143219e-22</v>
+        <v>5.076198006242589e-23</v>
       </c>
       <c r="C2" t="n">
-        <v>2.592621857977689e-20</v>
+        <v>1.213211323491979e-20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mitglieder</t>
+          <t>Versicherte</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.839091870469062e-21</v>
+        <v>1.498625352426491e-22</v>
       </c>
       <c r="C3" t="n">
-        <v>8.510814467955739e-19</v>
+        <v>1.790857296149657e-20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MGxRF</t>
+          <t>Mitglieder</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.029069213423288e-16</v>
+        <v>9.839091839299353e-21</v>
       </c>
       <c r="C4" t="n">
-        <v>1.746763246407429e-14</v>
+        <v>5.878857373981364e-19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ansprechpartner_Ja</t>
+          <t>Kontaktaufn_App_Ja</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.269062109258915e-08</v>
+        <v>7.719091151162731e-21</v>
       </c>
       <c r="C5" t="n">
-        <v>4.008869362254481e-06</v>
+        <v>5.878857373981364e-19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Quartal</t>
+          <t>Nutzung_von_Preisvergleichsportalen_Ja_zu_spterem_Zeitpunkt</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.429537288309153e-05</v>
+        <v>7.771531766136039e-19</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004946199017549668</v>
+        <v>2.762009828125251e-17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Berufsttigkeit_des_Befragten_RentnerPens</t>
+          <t>Kontaktaufn_Persnl_Kundenbereich_Nein</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008439008309088353</v>
+        <v>7.949657392585013e-19</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02433247395787142</v>
+        <v>2.762009828125251e-17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Berufsttigkeit_des_Befragten_RentnerPens</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>9.245221182009207e-19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2.762009828125251e-17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_quad_App_Ja</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>9.08381783786901e-19</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.762009828125251e-17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ansprechpartner_Nein</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.13657837622444e-18</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.265269390059219e-17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Personen_im_Haushalt_1</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0.001485572622061911</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.03671486623095865</v>
+      <c r="B11" t="n">
+        <v>2.42334574437872e-18</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.265269390059219e-17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Haushaltstypologie_Einpershaushalte</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2.42334574437872e-18</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.265269390059219e-17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SchnppchenJger_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4.730603916253981e-18</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.421786133205844e-17</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Guter_Ruf_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7.203345286186409e-18</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.324307325691194e-16</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_persnl_Kundenbereich_Ja</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1.334937316862263e-17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2.278928705214863e-16</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Informationskompetenz_Interesse_an_Gesundheitshemen_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.991996387494959e-17</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.173914244075301e-16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BIKStadtregion_in_Tausend_500_um</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3.057084946731451e-17</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.395848537956701e-16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Nutzung_Vermittlung_Arzttermine_Ja</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.126754190178406e-17</v>
+      </c>
+      <c r="C18" t="n">
+        <v>4.395848537956701e-16</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kundenbegeisterung_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.360508137589799e-17</v>
+      </c>
+      <c r="C19" t="n">
+        <v>4.462008027133122e-16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Alter_6069_Jahre</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5.735582893186141e-17</v>
+      </c>
+      <c r="C20" t="n">
+        <v>7.214759534060462e-16</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Informationskompetenz_Verstndlichkeit_von_Gesundheitsthemen_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.447595413045272e-16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.687708051162216e-15</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Kontaktformular_Website_Ja</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.482923392234583e-16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.687708051162216e-15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_App_Nein</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.715584879295743e-16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.782716461529054e-15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Haushaltstypologie_2_Pers_haushalte__50_J</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.713470685605603e-16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.782716461529054e-15</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Beruf_Angestellter</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.809911563151421e-16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.686275454372758e-15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Bonusprogramm_Nein</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.79046568559196e-16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2.686275454372758e-15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MGxRF</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.029069214207881e-16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2.784413623829552e-15</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Zuf_Umfang_der_OnlineServices_berz</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.796625504110365e-16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.36071664993473e-15</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Zuf_Nutzerfreundlichkeit_OnlineServices_berz</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3.975000790976012e-16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.392947103725954e-15</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Net_Promoter_Score_Promotoren</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>8.010567316086126e-16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>6.354256962305596e-15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Vorbereitung_auf_knftige_Herausf_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>8.241923256547009e-16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6.354256962305596e-15</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Zeit_nehmen_fr_Einkufe_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>8.128592011571731e-16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>6.354256962305596e-15</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Zeitgeme_Lsungen_zur_Digitalisierung_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.547795098822871e-16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>6.384134464433333e-15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Zuf_Individuelle_Beratung_Entt</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.069999523094266e-15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>7.74939048544029e-15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Geld_ist_derzeit_knapp_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.142733511457547e-15</v>
+      </c>
+      <c r="C35" t="n">
+        <v>7.960385267251389e-15</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Wertschtzung_als_Kunde_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.185759616323562e-15</v>
+      </c>
+      <c r="C36" t="n">
+        <v>7.960385267251389e-15</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Weiterempfehlungsabsicht_Ja</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.19905384778682e-15</v>
+      </c>
+      <c r="C37" t="n">
+        <v>7.960385267251389e-15</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Wiederwahlabsicht_Ja</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.644655778024978e-15</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1.06235873229181e-14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Wahltarif_Nein</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.730253646595686e-15</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1.088238477727287e-14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Zuf_Verstndlichkeit_der_schriftlichen_Unterlagen_berz</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.818863752955452e-15</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1.114637017836803e-14</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Sympathie_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.875241386491823e-15</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1.120456728428864e-14</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Bildungsstatus_Uni</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>3.292325718917428e-15</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.919184992246989e-14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Wechsel_geplant_Nein</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>3.781570160709114e-15</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.151893496213043e-14</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Nutzung_medizinische_Hotline_Ja</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>4.573545598275956e-15</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2.538901732703903e-14</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Kundenaufwand_Customer_Effort_Score_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>4.674128712927688e-15</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.538901732703903e-14</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Schriftlich_Nein</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>5.452655378302657e-15</v>
+      </c>
+      <c r="C46" t="n">
+        <v>2.8959658564763e-14</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Nutzung_Elektronische_Patientenakte_ePA_Ja</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>5.890261406975993e-15</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3.060374948407092e-14</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Kundenloyalitt_Ja</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>7.45611595943883e-15</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3.712524404803918e-14</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Anzahl_Endgerte_fr_Internetnutzung_5</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>7.315756742400203e-15</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.712524404803918e-14</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Anpassung_Zusatzbeitrag_Nein</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>8.365013413279699e-15</v>
+      </c>
+      <c r="C50" t="n">
+        <v>4.080077970967036e-14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Website_Ja</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>8.799846202971751e-15</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4.123849495118135e-14</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Geschftsstelle_Nein</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>8.693373798544058e-15</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4.123849495118135e-14</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Zuf_Leistungsumfang_berz</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>9.262631703453085e-15</v>
+      </c>
+      <c r="C53" t="n">
+        <v>4.257248032933244e-14</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Telefonisch_Nein</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.013220343576873e-14</v>
+      </c>
+      <c r="C54" t="n">
+        <v>4.569050228582502e-14</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Nutzung_DeutschlandCard_Nein</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.197406828386976e-14</v>
+      </c>
+      <c r="C55" t="n">
+        <v>5.229447884114835e-14</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Nutzung_Prventionsangebote_Nein</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1.242940399259175e-14</v>
+      </c>
+      <c r="C56" t="n">
+        <v>5.229447884114835e-14</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Anzahl_Endgerte_fr_Internetnutzung_3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.269071034638746e-14</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5.229447884114835e-14</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Leistungsanspruch_Nein</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.267831320950397e-14</v>
+      </c>
+      <c r="C58" t="n">
+        <v>5.229447884114835e-14</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Globalzufriedenheit_berz</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.268482993754642e-14</v>
+      </c>
+      <c r="C59" t="n">
+        <v>5.229447884114835e-14</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Bevorzugung_stationre_Geschfte_vor_Onlineshops_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1.566390497787167e-14</v>
+      </c>
+      <c r="C60" t="n">
+        <v>6.345208965612421e-14</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Newsletter_Nein</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.82227563623801e-14</v>
+      </c>
+      <c r="C61" t="n">
+        <v>7.258731284348073e-14</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Zuf_Informationen_zu_Gesundheitsthemen_berz</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1.934985243512286e-14</v>
+      </c>
+      <c r="C62" t="n">
+        <v>7.581335626220268e-14</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Bildungsstatus_Abi</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2.19431942675508e-14</v>
+      </c>
+      <c r="C63" t="n">
+        <v>8.458747467652648e-14</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Personen_im_Haushalt_2</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2.337277703412242e-14</v>
+      </c>
+      <c r="C64" t="n">
+        <v>8.866815414532154e-14</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ausprobieren_von_neuen_ProduktenLeistungen_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2.461891579597507e-14</v>
+      </c>
+      <c r="C65" t="n">
+        <v>9.193626367559442e-14</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Bevorzugung_stationre_Geschfte_vor_Onlineshops_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2.828832343280371e-14</v>
+      </c>
+      <c r="C66" t="n">
+        <v>1.040139892375398e-13</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Informationskompetenz_Interesse_an_Gesundheitshemen_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>2.958978289600708e-14</v>
+      </c>
+      <c r="C67" t="n">
+        <v>1.07150880487056e-13</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Vertrauen_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>3.017289584809438e-14</v>
+      </c>
+      <c r="C68" t="n">
+        <v>1.074021231300415e-13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Aktive_Betreuung_Nein</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>3.055792624620427e-14</v>
+      </c>
+      <c r="C69" t="n">
+        <v>1.074021231300415e-13</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_ADM_Nein</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3.537005014155176e-14</v>
+      </c>
+      <c r="C70" t="n">
+        <v>1.225136519395778e-13</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Zeit_nehmen_fr_Einkufe_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3.61979484725034e-14</v>
+      </c>
+      <c r="C71" t="n">
+        <v>1.235901383561188e-13</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ausreichende_Absicherung_Ja</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4.05777672597621e-14</v>
+      </c>
+      <c r="C72" t="n">
+        <v>1.365927658462414e-13</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Verlsslichkeit_in_schwierigen_Zeiten_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>4.612991840332163e-14</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1.531257013665815e-13</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Nutzung_von_Preisvergleichsportalen_Seltenekeine_Nutzung</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>5.078823780772704e-14</v>
+      </c>
+      <c r="C74" t="n">
+        <v>1.662792991239282e-13</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Persnl_Kundenbereich_Ja</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>6.201933784379475e-14</v>
+      </c>
+      <c r="C75" t="n">
+        <v>1.997160457490389e-13</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Videotelefonie_Nein</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>6.267239929363145e-14</v>
+      </c>
+      <c r="C76" t="n">
+        <v>1.997160457490389e-13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Haushaltsnettoeinkommen_in_Euro_25003999</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>6.703901393344234e-14</v>
+      </c>
+      <c r="C77" t="n">
+        <v>2.108200569749042e-13</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Wohnsituation_Mieter_einer_Wohnung</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>6.970468232568775e-14</v>
+      </c>
+      <c r="C78" t="n">
+        <v>2.131891429018639e-13</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Haushaltsnettoeinkommen_in_Euro_4000_und_mehr</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>6.999140688549534e-14</v>
+      </c>
+      <c r="C79" t="n">
+        <v>2.131891429018639e-13</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Verhltnis_zu_sozialen_Medien_Kein_Interesse</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>7.046837777927719e-14</v>
+      </c>
+      <c r="C80" t="n">
+        <v>2.131891429018639e-13</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Nutzung_Vermittlung_Arzttermine_Nein</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>8.574066079933718e-14</v>
+      </c>
+      <c r="C81" t="n">
+        <v>2.561502241380198e-13</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Anzahl_Endgerte_fr_Internetnutzung_1</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>8.87637698985697e-14</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2.619079136513353e-13</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Reklamation_Nein</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>9.377292383832677e-14</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2.733137658214646e-13</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Bevorzugung_von_regionalen_Produkten_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1.090439960574605e-13</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3.139941573220851e-13</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_EMail_Nein</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1.106581586046676e-13</v>
+      </c>
+      <c r="C85" t="n">
+        <v>3.148488084108996e-13</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_VideoOnlineberatung_Nein</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1.337552740002542e-13</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3.760883586595383e-13</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Informationskompetenz_Verstndlichkeit_von_Gesundheitsthemen_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1.477699221648606e-13</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4.106629232256011e-13</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Chat_Nein</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1.666518675673951e-13</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4.578137511334188e-13</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Nutzung_Smartphone_Ja</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1.716559548876519e-13</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4.662019683880547e-13</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Net_Promoter_Score_Passive</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1.768520275144858e-13</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.749172424265407e-13</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Nutzung_medizinische_Hotline_Nein</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1.817056533383264e-13</v>
+      </c>
+      <c r="C91" t="n">
+        <v>4.825294571984445e-13</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Nutzung_Payback_Ja</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1.908548098659909e-13</v>
+      </c>
+      <c r="C92" t="n">
+        <v>5.012560390985913e-13</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Zufriedenheit_PreisLeistungsVerhltnis_Zufr</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>2.001500124780178e-13</v>
+      </c>
+      <c r="C93" t="n">
+        <v>5.153785654938905e-13</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Zufriedenheit_PreisLeistungsVerhltnis_berz</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>2.005447974515976e-13</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5.153785654938905e-13</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Bekannte_Markenartikel_haben_eine_gute_Qualitt_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2.176912120158563e-13</v>
+      </c>
+      <c r="C95" t="n">
+        <v>5.534914858701026e-13</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ausprobieren_von_neuen_ProduktenLeistungen_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2.281608839772244e-13</v>
+      </c>
+      <c r="C96" t="n">
+        <v>5.740047502163857e-13</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Digitalisierung_ist_eher_positiv_als_negativ_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2.420113068296007e-13</v>
+      </c>
+      <c r="C97" t="n">
+        <v>6.025073159611935e-13</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Kontakt_aufgenommen_Nein</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2.569699829003612e-13</v>
+      </c>
+      <c r="C98" t="n">
+        <v>6.331528444658384e-13</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SchnppchenJger_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2.727465588502988e-13</v>
+      </c>
+      <c r="C99" t="n">
+        <v>6.65167628216545e-13</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Geschlecht_Weiblich</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2.903974901131754e-13</v>
+      </c>
+      <c r="C100" t="n">
+        <v>7.010606074449384e-13</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Bevorzugung_von_regionalen_Produkten_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3.035557371067004e-13</v>
+      </c>
+      <c r="C101" t="n">
+        <v>7.254982116850141e-13</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Geschlecht_Mnnlich</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3.582592034906161e-13</v>
+      </c>
+      <c r="C102" t="n">
+        <v>8.477618775669034e-13</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Legt_Wert_auf_Nachhaltigkeit_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>3.896830932570837e-13</v>
+      </c>
+      <c r="C103" t="n">
+        <v>9.13080973416108e-13</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sympathie_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4.675456019241455e-13</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1.084887367571561e-12</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Zuf_Umfang_der_OnlineServices_Zufr</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>5.485353619429196e-13</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1.260576456772671e-12</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Wohnsituation_Eigenes_Haus</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>6.863325826493953e-13</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1.562223688125766e-12</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Kontakt_aufgenommen_Ja</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>7.680740181439099e-13</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1.73178953147542e-12</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Nutzung_Payback_Nein</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>7.791323797732284e-13</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1.740305035194407e-12</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Alter_4049_Jahre</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1.055237318382278e-12</v>
+      </c>
+      <c r="C109" t="n">
+        <v>2.335201102716337e-12</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Bevorzugung_von_nachhaltigen_Produkten_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1.270791197796868e-12</v>
+      </c>
+      <c r="C110" t="n">
+        <v>2.78641372727937e-12</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Bevorzugung_von_nachhaltigen_Produkten_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1.466003010318949e-12</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3.185224722420261e-12</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Vertrauen_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1.698693661582242e-12</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3.657547613677081e-12</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Geld_ist_derzeit_knapp_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1.829248942500957e-12</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3.903486582658292e-12</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Qualitt_ist_wichtiger_als_Preis_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1.875506711462289e-12</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.966779681765371e-12</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Kundenaufwand_Customer_Effort_Score_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1.957993310616943e-12</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.104915800328503e-12</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Zuf_Nutzerfreundlichkeit_OnlineServices_Zufr</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>2.587706317011836e-12</v>
+      </c>
+      <c r="C116" t="n">
+        <v>5.377928780572424e-12</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Zuf_Leistungsumfang_Zufr</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2.883816017124269e-12</v>
+      </c>
+      <c r="C117" t="n">
+        <v>5.901089408130869e-12</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Vorbereitung_auf_knftige_Herausf_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2.888817827411346e-12</v>
+      </c>
+      <c r="C118" t="n">
+        <v>5.901089408130869e-12</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Kontaktformular_Website_Nein</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>3.03804614299979e-12</v>
+      </c>
+      <c r="C119" t="n">
+        <v>6.153330747262286e-12</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Verlsslichkeit_in_schwierigen_Zeiten_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>3.12967887571621e-12</v>
+      </c>
+      <c r="C120" t="n">
+        <v>6.285657573917431e-12</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Wertschtzung_als_Kunde_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>3.241706787406822e-12</v>
+      </c>
+      <c r="C121" t="n">
+        <v>6.456399351585254e-12</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Nutzung_Elektronische_Patientenakte_ePA_Nein</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>3.271263230593426e-12</v>
+      </c>
+      <c r="C122" t="n">
+        <v>6.461420761254783e-12</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kundenaufwand_Customer_Effort_Score_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>3.873547254684981e-12</v>
+      </c>
+      <c r="C123" t="n">
+        <v>7.588342572702545e-12</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Dauer_der_Kundenbeziehung_10_bis_unter_15_Jahre</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>4.338895233181242e-12</v>
+      </c>
+      <c r="C124" t="n">
+        <v>8.43086146935217e-12</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Bekannte_Markenartikel_haben_eine_gute_Qualitt_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4.639427373952391e-12</v>
+      </c>
+      <c r="C125" t="n">
+        <v>8.942122115924365e-12</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Zuf_Aktive_Betreuung_Zufr</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>5.048990541732665e-12</v>
+      </c>
+      <c r="C126" t="n">
+        <v>9.653669915792856e-12</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>BIKStadtregion_in_Tausend_20_bu_100</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>5.134994342038344e-12</v>
+      </c>
+      <c r="C127" t="n">
+        <v>9.740187680533049e-12</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Nutzung_Smartphone_Nein</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>6.600126748814658e-12</v>
+      </c>
+      <c r="C128" t="n">
+        <v>1.242071096824176e-11</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Zuf_Individuelle_Beratung_berz</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>7.310371527066088e-12</v>
+      </c>
+      <c r="C129" t="n">
+        <v>1.364983433569371e-11</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Berufsttigkeit_des_Befragten_Ja</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>7.452692163712736e-12</v>
+      </c>
+      <c r="C130" t="n">
+        <v>1.380770098548329e-11</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Gebiet_West_ohne_Berlin</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>7.515406109315834e-12</v>
+      </c>
+      <c r="C131" t="n">
+        <v>1.381678507789603e-11</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Zuf_Aktive_Betreuung_Entt</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>7.888162391184602e-12</v>
+      </c>
+      <c r="C132" t="n">
+        <v>1.43913802404055e-11</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Kundenbegeisterung_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>8.743017745117049e-12</v>
+      </c>
+      <c r="C133" t="n">
+        <v>1.571113715099981e-11</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Wertschtzung_als_Kunde_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>8.683119257338737e-12</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.571113715099981e-11</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Bonusprogramm_Ja</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1.21767012885252e-11</v>
+      </c>
+      <c r="C135" t="n">
+        <v>2.171814632804121e-11</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Haushaltstypologie_2_Pers_haushalte_bis_50_J</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1.614277108364216e-11</v>
+      </c>
+      <c r="C136" t="n">
+        <v>2.849952484024457e-11</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Beruf_SelbststndigFreiberuflichLeiterin_von_UnternehmenLandwirtin</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>1.621730283796344e-11</v>
+      </c>
+      <c r="C137" t="n">
+        <v>2.849952484024457e-11</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Leistungsanspruch_Ja</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1.73724981157526e-11</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.030676678587498e-11</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Telefonisch_Ja</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1.78871751123766e-11</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.097851341926092e-11</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Zuf_Individuelle_Beratung_Zufr</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2.029652999361624e-11</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.489835013290851e-11</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Zeitgeme_Lsungen_zur_Digitalisierung_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2.15817689094446e-11</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.684316263826614e-11</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_EMail_Ja</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2.629644808029486e-11</v>
+      </c>
+      <c r="C142" t="n">
+        <v>4.457341199425866e-11</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Bildungsstatus_Weiterf_Schule</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2.660242522498921e-11</v>
+      </c>
+      <c r="C143" t="n">
+        <v>4.477450442797479e-11</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Kundenbegeisterung_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2.780784237507263e-11</v>
+      </c>
+      <c r="C144" t="n">
+        <v>4.647604424924726e-11</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Arbeitswochenstunden_40_bu_45</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>3.425803088108008e-11</v>
+      </c>
+      <c r="C145" t="n">
+        <v>5.685881514290373e-11</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Nutzung_Prventionsangebote_Ja</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>6.045819741409439e-11</v>
+      </c>
+      <c r="C146" t="n">
+        <v>9.965178746185212e-11</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Digitalisierung_ist_eher_positiv_als_negativ_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>6.345135729105703e-11</v>
+      </c>
+      <c r="C147" t="n">
+        <v>1.038690026887851e-10</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Verhltnis_zu_sozialen_Medien_Reaktion_auf_andere_Beitrge</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>6.668762712900556e-11</v>
+      </c>
+      <c r="C148" t="n">
+        <v>1.084241012505601e-10</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Newsletter_Ja</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>7.179072017323514e-11</v>
+      </c>
+      <c r="C149" t="n">
+        <v>1.159323116311027e-10</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_Website_Nein</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>8.461663173421464e-11</v>
+      </c>
+      <c r="C150" t="n">
+        <v>1.357273488891094e-10</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Verlsslichkeit_in_schwierigen_Zeiten_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>8.907614863773613e-11</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1.419279968294596e-10</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Aktive_Betreuung_Ja</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1.048511166246699e-10</v>
+      </c>
+      <c r="C152" t="n">
+        <v>1.659564031344114e-10</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Zuf_Verstndlichkeit_der_schriftlichen_Unterlagen_Zufr</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1.365053355256661e-10</v>
+      </c>
+      <c r="C153" t="n">
+        <v>2.146366788857513e-10</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Legt_Wert_auf_Nachhaltigkeit_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1.786092547126181e-10</v>
+      </c>
+      <c r="C154" t="n">
+        <v>2.790039991916061e-10</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Arbeitswochenstunden_20_bu_30</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1.888294412715463e-10</v>
+      </c>
+      <c r="C155" t="n">
+        <v>2.930534835318154e-10</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Globalzufriedenheit_Zufr</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2.026181756925842e-10</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3.124241547775976e-10</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Bevorzugung_stationre_Geschfte_vor_Onlineshops_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2.934791279942261e-10</v>
+      </c>
+      <c r="C157" t="n">
+        <v>4.496250742988464e-10</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Nutzung_von_soz_Netzwerken_Ja</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>3.055535836977748e-10</v>
+      </c>
+      <c r="C158" t="n">
+        <v>4.651420796418355e-10</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_VideoOnlineberatung_Ja</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>3.137918321316462e-10</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4.746597967054649e-10</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Verhltnis_zu_sozialen_Medien_Verfassen_eigener_Beitrge</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>3.494025838304255e-10</v>
+      </c>
+      <c r="C160" t="n">
+        <v>5.25202626009256e-10</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Guter_Ruf_Weitgehend</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>3.673970534553899e-10</v>
+      </c>
+      <c r="C161" t="n">
+        <v>5.487993485989887e-10</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>BIKStadtregion_in_Tausend_100_bu_500</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>5.463910345205718e-10</v>
+      </c>
+      <c r="C162" t="n">
+        <v>8.111022189466872e-10</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Nutzung_DeutschlandCard_Ja</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>5.995419482998668e-10</v>
+      </c>
+      <c r="C163" t="n">
+        <v>8.845094175535072e-10</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Verhltnis_zu_sozialen_Medien_Lesen_von_Beitrgen</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>6.776244569388992e-10</v>
+      </c>
+      <c r="C164" t="n">
+        <v>9.935720564932327e-10</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Zuf_Aktive_Betreuung_berz</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>6.976970582803654e-10</v>
+      </c>
+      <c r="C165" t="n">
+        <v>1.016765834932972e-09</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Anzahl_Endgerte_fr_Internetnutzung_2</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>7.290253670391715e-10</v>
+      </c>
+      <c r="C166" t="n">
+        <v>1.055982198317345e-09</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Zuf_Informationen_zu_Gesundheitsthemen_Zufr</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>7.539298742768284e-10</v>
+      </c>
+      <c r="C167" t="n">
+        <v>1.08547734910941e-09</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Arbeitswochenstunden_30_bu_40</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>9.243780510198883e-10</v>
+      </c>
+      <c r="C168" t="n">
+        <v>1.322912300561397e-09</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Zuf_Schnelligkeit_der_Bearbeitung_Zufr</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1.544291508741329e-09</v>
+      </c>
+      <c r="C169" t="n">
+        <v>2.196938515411772e-09</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Qualitt_ist_wichtiger_als_Preis_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1.871771596291425e-09</v>
+      </c>
+      <c r="C170" t="n">
+        <v>2.647061606589648e-09</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Alter_1629_Jahre</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1.981911061134267e-09</v>
+      </c>
+      <c r="C171" t="n">
+        <v>2.786333785947588e-09</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Wiederwahlabsicht_Nein</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>2.245777278339343e-09</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.13883490949183e-09</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Informationskompetenz_Interesse_an_Gesundheitshemen_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>3.507109379064211e-09</v>
+      </c>
+      <c r="C173" t="n">
+        <v>4.873250823234572e-09</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Weiterempfehlungsabsicht_Evtl</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3.616890846759514e-09</v>
+      </c>
+      <c r="C174" t="n">
+        <v>4.996745158240022e-09</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Personen_im_Haushalt_34</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>4.087200955207284e-09</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5.60433817589101e-09</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Sympathie_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>4.103594898664965e-09</v>
+      </c>
+      <c r="C176" t="n">
+        <v>5.60433817589101e-09</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Zuf_Informationen_zu_Gesundheitsthemen_Entt</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>5.293049205421629e-09</v>
+      </c>
+      <c r="C177" t="n">
+        <v>7.187720227816871e-09</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Haushaltstypologie_Mehrpershaushalte_quad_o_K</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>5.375082041565538e-09</v>
+      </c>
+      <c r="C178" t="n">
+        <v>7.257879140870981e-09</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Chat_Ja</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>5.903868052169097e-09</v>
+      </c>
+      <c r="C179" t="n">
+        <v>7.92710373296862e-09</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Ausprobieren_von_neuen_ProduktenLeistungen_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>7.540680157823555e-09</v>
+      </c>
+      <c r="C180" t="n">
+        <v>1.006828244536218e-08</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Wechsel_geplant_Ja</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>7.767641613642174e-09</v>
+      </c>
+      <c r="C181" t="n">
+        <v>1.0313701920336e-08</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Zuf_Schnelligkeit_der_Bearbeitung_berz</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1.166760636668419e-08</v>
+      </c>
+      <c r="C182" t="n">
+        <v>1.540639735711338e-08</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Bildungsstatus_Hauptschuleo_Schulabschl</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1.801015384161398e-08</v>
+      </c>
+      <c r="C183" t="n">
+        <v>2.365069652827331e-08</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Bevorzugung_von_regionalen_Produkten_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2.052487599041682e-08</v>
+      </c>
+      <c r="C184" t="n">
+        <v>2.680571235906895e-08</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Haushaltstypologie_Mit_Kindern_unter_18_J</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>2.4201341618426e-08</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3.143543829784681e-08</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Leistungen_abgelehnt_Nein</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2.629951577092349e-08</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.3976131185139e-08</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Geld_ist_derzeit_knapp_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>5.078951703894437e-08</v>
+      </c>
+      <c r="C187" t="n">
+        <v>6.526179877584788e-08</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Zuf_Nutzerfreundlichkeit_OnlineServices_Entt</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>5.60667746281448e-08</v>
+      </c>
+      <c r="C188" t="n">
+        <v>7.165753548730806e-08</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Anzahl_Endgerte_fr_Internetnutzung_4</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>1.091489894307958e-07</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1.387585557125542e-07</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Informationskompetenz_Verstndlichkeit_von_Gesundheitsthemen_Eher_nichtberh_nicht</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>1.244537428492565e-07</v>
+      </c>
+      <c r="C190" t="n">
+        <v>1.573780134442979e-07</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Zufriedenheit_PreisLeistungsVerhltnis_Entt</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1.561897858030743e-07</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1.964703095101829e-07</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Alter_3039_Jahre</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>1.600490547223796e-07</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2.00270806694496e-07</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_quad_App_Nein</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1.629382147736324e-07</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2.028241319317612e-07</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Kontaktaufn_Schriftlich_Ja</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2.588186496985388e-07</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.205059962588122e-07</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Haushaltsnettoeinkommen_in_Euro_15001999</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>5.388199088513934e-07</v>
+      </c>
+      <c r="C195" t="n">
+        <v>6.638039083272321e-07</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SchnppchenJger_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>8.955750175605561e-07</v>
+      </c>
+      <c r="C196" t="n">
+        <v>1.0976534830614e-06</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Dauer_der_Kundenbeziehung_5_bis_unter_10_Jahre</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1.183060102206058e-06</v>
+      </c>
+      <c r="C197" t="n">
+        <v>1.442609002179836e-06</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Alter_5059_Jahre</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.19285910381739e-06</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1.447174242702316e-06</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Nutzung_quad_persnl_Kundenbereich_Nein</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>1.224555142880894e-06</v>
+      </c>
+      <c r="C199" t="n">
+        <v>1.478124642164312e-06</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Dauer_der_Kundenbeziehung_20_bis_unter_30_Jahre</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1.340852676677022e-06</v>
+      </c>
+      <c r="C200" t="n">
+        <v>1.610370802642252e-06</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Net_Promoter_Score_Detraktoren</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>4.763944683575858e-06</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5.69291389687315e-06</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Haushaltsnettoeinkommen_in_Euro_20002499</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>8.390362893922917e-06</v>
+      </c>
+      <c r="C202" t="n">
+        <v>9.97660065496307e-06</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Quartal</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1.429537288309148e-05</v>
+      </c>
+      <c r="C203" t="n">
+        <v>1.691383227256863e-05</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>BIKStadtregion_in_Tausend_5_bu_20</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2.203524104776663e-05</v>
+      </c>
+      <c r="C204" t="n">
+        <v>2.594296852421785e-05</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Haushaltstypologie_Mit_Kindern_bis_9_J</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>4.650559111717543e-05</v>
+      </c>
+      <c r="C205" t="n">
+        <v>5.448449155394573e-05</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Nutzung_von_Preisvergleichsportalen_Ja_zu_Beginn_der_Recherche</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>0.001198216365232442</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.001396944933124652</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Zeit_nehmen_fr_Einkufe_Voll_und_ganz</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0.00206461871166486</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.002395358602368454</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Zusatzbeitrag</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>0.01038189032940727</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.0119868202354026</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ZB_mean</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0.02747771666383523</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.03157295328200298</v>
       </c>
     </row>
   </sheetData>
